--- a/output/2026-10-05_20_Croazia_Međimurska_Cleaning.xlsx
+++ b/output/2026-10-05_20_Croazia_Međimurska_Cleaning.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Punto vendita/distribuzione Würth, Ulica Zrinsko Frankopanska 17; distributore B2B utensili e attrezzature professionali incl. prodotti pulizia officina.</t>
+          <t>Punto vendita/distribuzione Würth, Ulica Zrinsko Frankopanska 17; distributore B2B utensili e attrezzature professionali incl. prodotti pulizia officina. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
